--- a/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/SRFormer2/SRFormer2+50T+50EP+optim_purn/params_vs_psnr_analysis/SRFormer_hutcn_hyperopt_study_full.xlsx
+++ b/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/SRFormer2/SRFormer2+50T+50EP+optim_purn/params_vs_psnr_analysis/SRFormer_hutcn_hyperopt_study_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,55 +446,60 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>flops_G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>hp_nf</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>hp_num_heads</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>hp_window_size</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>hp_num_blocks</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>hp_ffn_ratio</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>hp_patch_size</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hp_optimizer</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>hp_scheduler</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>hp_loss</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>hp_lr</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>hp_weight_decay</t>
         </is>
@@ -511,42 +516,45 @@
         <v>28.68567848205566</v>
       </c>
       <c r="D2" t="n">
+        <v>0.532461312</v>
+      </c>
+      <c r="E2" t="n">
         <v>64</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
       <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
         <v>12</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>3</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1.5</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>128</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>step</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>0.0002157696745589684</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>3.972110727381911e-06</v>
       </c>
     </row>
@@ -561,42 +569,45 @@
         <v>27.63242301940918</v>
       </c>
       <c r="D3" t="n">
+        <v>0.70953912</v>
+      </c>
+      <c r="E3" t="n">
         <v>80</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>8</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>12</v>
       </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
       <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>160</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fixed</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>0.0003946212980759095</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>0.000483595277646595</v>
       </c>
     </row>
@@ -611,42 +622,45 @@
         <v>27.29326095581055</v>
       </c>
       <c r="D4" t="n">
+        <v>0.853496012</v>
+      </c>
+      <c r="E4" t="n">
         <v>88</v>
       </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
       <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
         <v>16</v>
       </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
       <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
         <v>1.5</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>192</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>1.573468512939365e-05</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>0.0003884277754703142</v>
       </c>
     </row>
@@ -661,42 +675,45 @@
         <v>27.70898895263672</v>
       </c>
       <c r="D5" t="n">
+        <v>0.861195456</v>
+      </c>
+      <c r="E5" t="n">
         <v>96</v>
       </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
       <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
         <v>12</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>1.5</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>128</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>step</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>4.979987773685082e-05</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>0.0001847793417351927</v>
       </c>
     </row>
@@ -711,42 +728,45 @@
         <v>27.91423835754394</v>
       </c>
       <c r="D6" t="n">
+        <v>0.234716208</v>
+      </c>
+      <c r="E6" t="n">
         <v>48</v>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
         <v>128</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>3.74626115583896e-05</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>0.0006741074265640696</v>
       </c>
     </row>
@@ -761,42 +781,45 @@
         <v>27.77197608947754</v>
       </c>
       <c r="D7" t="n">
+        <v>0.464754432</v>
+      </c>
+      <c r="E7" t="n">
         <v>64</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
         <v>1.5</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>192</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>4.215533166949115e-05</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>7.887102624766475e-05</v>
       </c>
     </row>
@@ -811,42 +834,45 @@
         <v>27.95370635986328</v>
       </c>
       <c r="D8" t="n">
+        <v>0.88709344</v>
+      </c>
+      <c r="E8" t="n">
         <v>96</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>8</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>16</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
       <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
         <v>160</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>step</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>8.775452610882289e-05</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>3.88107231640948e-05</v>
       </c>
     </row>
@@ -861,42 +887,45 @@
         <v>29.67362060546875</v>
       </c>
       <c r="D9" t="n">
+        <v>0.444021868</v>
+      </c>
+      <c r="E9" t="n">
         <v>56</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>8</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>16</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>4</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>160</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>0.0001621702307943825</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>5.149288946949016e-06</v>
       </c>
     </row>
@@ -911,42 +940,45 @@
         <v>20.93247566223145</v>
       </c>
       <c r="D10" t="n">
+        <v>0.394269952</v>
+      </c>
+      <c r="E10" t="n">
         <v>64</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>8</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>4</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
         <v>160</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>0.0004175380307518434</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>0.0005553837526912237</v>
       </c>
     </row>
@@ -961,10 +993,10 @@
         <v>28.98331031799317</v>
       </c>
       <c r="D11" t="n">
+        <v>0.6259269119999999</v>
+      </c>
+      <c r="E11" t="n">
         <v>64</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
@@ -973,30 +1005,33 @@
         <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
         <v>128</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>4.080982033012063e-05</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>7.599334001601099e-06</v>
       </c>
     </row>
@@ -1011,42 +1046,45 @@
         <v>30.16123313903809</v>
       </c>
       <c r="D12" t="n">
+        <v>2.031102976</v>
+      </c>
+      <c r="E12" t="n">
         <v>128</v>
-      </c>
-      <c r="E12" t="n">
-        <v>8</v>
       </c>
       <c r="F12" t="n">
         <v>8</v>
       </c>
       <c r="G12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" t="n">
         <v>4</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>160</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>0.0001286066697250772</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>1.217404417807554e-06</v>
       </c>
     </row>
@@ -1061,42 +1099,45 @@
         <v>30.14192695617676</v>
       </c>
       <c r="D13" t="n">
+        <v>2.031102976</v>
+      </c>
+      <c r="E13" t="n">
         <v>128</v>
-      </c>
-      <c r="E13" t="n">
-        <v>8</v>
       </c>
       <c r="F13" t="n">
         <v>8</v>
       </c>
       <c r="G13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H13" t="n">
         <v>4</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>160</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>0.000128656810829938</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>1.051750379566391e-06</v>
       </c>
     </row>
@@ -1111,42 +1152,45 @@
         <v>30.14807777404785</v>
       </c>
       <c r="D14" t="n">
+        <v>2.031102976</v>
+      </c>
+      <c r="E14" t="n">
         <v>128</v>
-      </c>
-      <c r="E14" t="n">
-        <v>8</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" t="n">
         <v>4</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>160</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>0.0001132358814943246</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>1.193022088047211e-06</v>
       </c>
     </row>
@@ -1161,42 +1205,45 @@
         <v>29.98004493713379</v>
       </c>
       <c r="D15" t="n">
+        <v>1.834355712</v>
+      </c>
+      <c r="E15" t="n">
         <v>128</v>
-      </c>
-      <c r="E15" t="n">
-        <v>8</v>
       </c>
       <c r="F15" t="n">
         <v>8</v>
       </c>
       <c r="G15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" t="n">
         <v>3</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>1</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>160</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>8.899836557699988e-05</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>1.607325516266553e-06</v>
       </c>
     </row>
@@ -1211,42 +1258,45 @@
         <v>30.27306976318359</v>
       </c>
       <c r="D16" t="n">
+        <v>1.42148856</v>
+      </c>
+      <c r="E16" t="n">
         <v>112</v>
-      </c>
-      <c r="E16" t="n">
-        <v>8</v>
       </c>
       <c r="F16" t="n">
         <v>8</v>
       </c>
       <c r="G16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" t="n">
         <v>3</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>160</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>0.0002398839178049098</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>1.783129864452785e-05</v>
       </c>
     </row>
@@ -1261,42 +1311,45 @@
         <v>30.24274101257324</v>
       </c>
       <c r="D17" t="n">
+        <v>1.418695056</v>
+      </c>
+      <c r="E17" t="n">
         <v>112</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>8</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>6</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>3</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>160</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>0.0002361301297838682</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>1.798197404980717e-05</v>
       </c>
     </row>
@@ -1311,42 +1364,45 @@
         <v>30.10407485961914</v>
       </c>
       <c r="D18" t="n">
+        <v>1.418695056</v>
+      </c>
+      <c r="E18" t="n">
         <v>112</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>8</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>6</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>3</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>192</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>0.0002315377329110376</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>1.242679035117956e-05</v>
       </c>
     </row>
@@ -1361,42 +1417,45 @@
         <v>30.3240592956543</v>
       </c>
       <c r="D19" t="n">
+        <v>1.599070608</v>
+      </c>
+      <c r="E19" t="n">
         <v>112</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>8</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>6</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>3</v>
       </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
       <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
         <v>160</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>0.0002720063310043572</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>2.29291695208233e-05</v>
       </c>
     </row>
@@ -1411,42 +1470,45 @@
         <v>30.33113746643066</v>
       </c>
       <c r="D20" t="n">
+        <v>1.59904728</v>
+      </c>
+      <c r="E20" t="n">
         <v>112</v>
       </c>
-      <c r="E20" t="n">
-        <v>2</v>
-      </c>
       <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
         <v>6</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>3</v>
       </c>
-      <c r="H20" t="n">
-        <v>2</v>
-      </c>
       <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
         <v>160</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>0.0004647522481492764</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>6.215095894860666e-05</v>
       </c>
     </row>
@@ -1461,42 +1523,45 @@
         <v>30.30764122009277</v>
       </c>
       <c r="D21" t="n">
+        <v>1.388091852</v>
+      </c>
+      <c r="E21" t="n">
         <v>104</v>
       </c>
-      <c r="E21" t="n">
-        <v>2</v>
-      </c>
       <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
         <v>6</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>3</v>
       </c>
-      <c r="H21" t="n">
-        <v>2</v>
-      </c>
       <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
         <v>160</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>0.0004896935041724372</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>0.0001072445894704732</v>
       </c>
     </row>
@@ -1511,42 +1576,45 @@
         <v>30.3703727722168</v>
       </c>
       <c r="D22" t="n">
+        <v>1.388091852</v>
+      </c>
+      <c r="E22" t="n">
         <v>104</v>
       </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
       <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
         <v>6</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>3</v>
       </c>
-      <c r="H22" t="n">
-        <v>2</v>
-      </c>
       <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
         <v>160</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>0.0004907822809058925</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>0.0001291189366036307</v>
       </c>
     </row>
@@ -1561,42 +1629,45 @@
         <v>30.28800964355469</v>
       </c>
       <c r="D23" t="n">
+        <v>1.388091852</v>
+      </c>
+      <c r="E23" t="n">
         <v>104</v>
       </c>
-      <c r="E23" t="n">
-        <v>2</v>
-      </c>
       <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
         <v>6</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>3</v>
       </c>
-      <c r="H23" t="n">
-        <v>2</v>
-      </c>
       <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
         <v>160</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>0.0002966288315522379</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>0.0001749990918135078</v>
       </c>
     </row>
@@ -1611,42 +1682,45 @@
         <v>30.36462135314941</v>
       </c>
       <c r="D24" t="n">
+        <v>1.824885612</v>
+      </c>
+      <c r="E24" t="n">
         <v>120</v>
       </c>
-      <c r="E24" t="n">
-        <v>2</v>
-      </c>
       <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
         <v>6</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>3</v>
       </c>
-      <c r="H24" t="n">
-        <v>2</v>
-      </c>
       <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
         <v>160</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>0.0002985722800361831</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>3.572296853046735e-05</v>
       </c>
     </row>
@@ -1661,42 +1735,45 @@
         <v>30.37883644104004</v>
       </c>
       <c r="D25" t="n">
+        <v>1.583651628</v>
+      </c>
+      <c r="E25" t="n">
         <v>120</v>
       </c>
-      <c r="E25" t="n">
-        <v>2</v>
-      </c>
       <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
         <v>6</v>
       </c>
-      <c r="G25" t="n">
-        <v>2</v>
-      </c>
       <c r="H25" t="n">
         <v>2</v>
       </c>
       <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
         <v>160</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>0.0004867605338320274</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>4.157045581679513e-05</v>
       </c>
     </row>
@@ -1711,42 +1788,45 @@
         <v>30.45349769592285</v>
       </c>
       <c r="D26" t="n">
+        <v>1.824885612</v>
+      </c>
+      <c r="E26" t="n">
         <v>120</v>
       </c>
-      <c r="E26" t="n">
-        <v>2</v>
-      </c>
       <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
         <v>6</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>3</v>
       </c>
-      <c r="H26" t="n">
-        <v>2</v>
-      </c>
       <c r="I26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" t="n">
         <v>160</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>0.0004806223622243637</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>6.415362565853938e-05</v>
       </c>
     </row>
@@ -1761,42 +1841,45 @@
         <v>30.32417602539062</v>
       </c>
       <c r="D27" t="n">
+        <v>1.824885612</v>
+      </c>
+      <c r="E27" t="n">
         <v>120</v>
       </c>
-      <c r="E27" t="n">
-        <v>2</v>
-      </c>
       <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
         <v>6</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>3</v>
       </c>
-      <c r="H27" t="n">
-        <v>2</v>
-      </c>
       <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
         <v>160</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>0.0003508964984375244</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>5.562969337557059e-05</v>
       </c>
     </row>
@@ -1811,42 +1894,45 @@
         <v>30.30941543579102</v>
       </c>
       <c r="D28" t="n">
+        <v>1.2058587</v>
+      </c>
+      <c r="E28" t="n">
         <v>104</v>
       </c>
-      <c r="E28" t="n">
-        <v>2</v>
-      </c>
       <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="n">
         <v>6</v>
       </c>
-      <c r="G28" t="n">
-        <v>2</v>
-      </c>
       <c r="H28" t="n">
         <v>2</v>
       </c>
       <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
         <v>160</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>0.0003537625431541822</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>0.0002983729436353502</v>
       </c>
     </row>
@@ -1861,42 +1947,45 @@
         <v>30.2251350402832</v>
       </c>
       <c r="D29" t="n">
+        <v>1.142319564</v>
+      </c>
+      <c r="E29" t="n">
         <v>88</v>
       </c>
-      <c r="E29" t="n">
-        <v>2</v>
-      </c>
       <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
         <v>6</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>4</v>
       </c>
-      <c r="H29" t="n">
-        <v>2</v>
-      </c>
       <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
         <v>192</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>0.0003791158791211792</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>4.735693065210736e-05</v>
       </c>
     </row>
@@ -1911,42 +2000,45 @@
         <v>30.36607513427735</v>
       </c>
       <c r="D30" t="n">
+        <v>1.59904728</v>
+      </c>
+      <c r="E30" t="n">
         <v>112</v>
       </c>
-      <c r="E30" t="n">
-        <v>2</v>
-      </c>
       <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
         <v>6</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>3</v>
       </c>
-      <c r="H30" t="n">
-        <v>2</v>
-      </c>
       <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
         <v>160</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>0.0004974381354623576</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>0.000834657328983546</v>
       </c>
     </row>
@@ -1961,42 +2053,45 @@
         <v>30.35539321899414</v>
       </c>
       <c r="D31" t="n">
+        <v>1.388091852</v>
+      </c>
+      <c r="E31" t="n">
         <v>104</v>
       </c>
-      <c r="E31" t="n">
-        <v>2</v>
-      </c>
       <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
         <v>6</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>3</v>
       </c>
-      <c r="H31" t="n">
-        <v>2</v>
-      </c>
       <c r="I31" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" t="n">
         <v>160</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>0.000385106666417719</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>0.0007841339661006904</v>
       </c>
     </row>
@@ -2011,42 +2106,45 @@
         <v>30.4514907836914</v>
       </c>
       <c r="D32" t="n">
+        <v>2.066119596</v>
+      </c>
+      <c r="E32" t="n">
         <v>120</v>
       </c>
-      <c r="E32" t="n">
-        <v>2</v>
-      </c>
       <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
         <v>6</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>4</v>
       </c>
-      <c r="H32" t="n">
-        <v>2</v>
-      </c>
       <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
         <v>160</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>0.0004039946922743858</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>0.0005537111276384507</v>
       </c>
     </row>
@@ -2061,42 +2159,45 @@
         <v>30.28403930664063</v>
       </c>
       <c r="D33" t="n">
+        <v>0.780427756</v>
+      </c>
+      <c r="E33" t="n">
         <v>72</v>
       </c>
-      <c r="E33" t="n">
-        <v>2</v>
-      </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G33" t="n">
         <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
         <v>128</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>AdamW</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>0.0004987788751500371</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>0.0005670658924197496</v>
       </c>
     </row>
